--- a/artfynd/A 63367-2021 artfynd.xlsx
+++ b/artfynd/A 63367-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63367-2021 artfynd.xlsx
+++ b/artfynd/A 63367-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>76753434</v>
+        <v>76753411</v>
       </c>
       <c r="B2" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>102118</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>292774.7660447826</v>
+        <v>292775</v>
       </c>
       <c r="R2" t="n">
-        <v>6510762.03955829</v>
+        <v>6510762</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-06-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-06-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,55 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>76753353</v>
+        <v>76753344</v>
       </c>
       <c r="B3" t="n">
-        <v>56632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kornbyberget, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>292775.8066600361</v>
+        <v>292776</v>
       </c>
       <c r="R3" t="n">
-        <v>6510761.984004228</v>
+        <v>6510762</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-05-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-06-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-05-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-06-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,50 +877,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>76753423</v>
+        <v>76753426</v>
       </c>
       <c r="B4" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>102623</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kornbyberget, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>292774.7660447826</v>
+        <v>292775</v>
       </c>
       <c r="R4" t="n">
-        <v>6510762.03955829</v>
+        <v>6510762</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,22 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,32 +983,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>76753405</v>
+        <v>76753410</v>
       </c>
       <c r="B5" t="n">
-        <v>56521</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103035</v>
+        <v>102977</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1068,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>292774.7660447826</v>
+        <v>292775</v>
       </c>
       <c r="R5" t="n">
-        <v>6510762.03955829</v>
+        <v>6510762</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,22 +1048,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,15 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>76753352</v>
+        <v>76753357</v>
       </c>
       <c r="B6" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,21 +1095,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>292775.8066600361</v>
+        <v>292776</v>
       </c>
       <c r="R6" t="n">
-        <v>6510761.984004228</v>
+        <v>6510762</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,22 +1154,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2012-05-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-06-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2012-05-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-06-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,6 +1183,940 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>76753443</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58497</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kornbyberget, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>292775</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6510762</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2016-05-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2016-05-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sofia Willebrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sofia Willebrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>76753353</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kornbyberget, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>292776</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6510762</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2012-05-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2012-05-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sofia Willebrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sofia Willebrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>76753371</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kornbyberget, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>292776</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6510762</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sofia Willebrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sofia Willebrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>76753454</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kornbyberget, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>292775</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6510762</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-05-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-05-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sofia Willebrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sofia Willebrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>76753352</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kornbyberget, Boh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>292776</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6510762</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2012-05-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2012-05-15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sofia Willebrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sofia Willebrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>76753423</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kornbyberget, Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>292775</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6510762</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sofia Willebrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sofia Willebrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>76753391</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kornbyberget, Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>292776</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6510762</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sofia Willebrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sofia Willebrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>76753430</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kornbyberget, Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>292775</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6510762</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2016-06-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2016-06-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sofia Willebrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sofia Willebrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>76753405</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kornbyberget, Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>292775</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6510762</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sofia Willebrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sofia Willebrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 63367-2021 artfynd.xlsx
+++ b/artfynd/A 63367-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76753411</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76753344</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76753426</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76753410</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76753357</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76753443</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76753353</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1500,6 +1540,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76753371</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1606,6 +1651,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76753454</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76753352</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1813,6 +1868,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76753423</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1914,6 +1974,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76753391</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2020,6 +2085,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76753430</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2121,8 +2191,29 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76753405</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>